--- a/outputs/daily/predictions_2026-06-22.xlsx
+++ b/outputs/daily/predictions_2026-06-22.xlsx
@@ -843,31 +843,31 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2.002781801010743</v>
+        <v>2.008152727419448</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7857332154480205</v>
+        <v>0.7858622890393159</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6558159732475818</v>
+        <v>0.6586930352463313</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2192351573767571</v>
+        <v>0.2171978379195809</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1249488693756611</v>
+        <v>0.1241091268340878</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4889977496526239</v>
+        <v>0.4913918286267711</v>
       </c>
       <c r="R2" t="n">
-        <v>1.896171989647957</v>
+        <v>1.905937310391057</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7338280103520426</v>
+        <v>0.7340626896089432</v>
       </c>
       <c r="T2" t="n">
         <v>0.7296802574398824</v>
@@ -885,58 +885,58 @@
         <v>0.5022518068231259</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6488662978685429</v>
+        <v>0.649952597427735</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2231122317259763</v>
+        <v>0.2224980526191161</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.128021470405481</v>
+        <v>0.1275493499531488</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5278001231378084</v>
+        <v>0.5291143634425087</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4721998768621916</v>
+        <v>0.4708856365574913</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4804471599188979</v>
+        <v>0.4808658080201872</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.519552840081102</v>
+        <v>0.5191341919798127</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.65077</v>
+        <v>0.651695</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.22173</v>
+        <v>0.221165</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1275</v>
+        <v>0.12714</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.52746</v>
+        <v>0.52896</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.4798</v>
+        <v>0.48015</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.004215</v>
+        <v>2.00959</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.783505</v>
+        <v>0.783695</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.78772</v>
+        <v>2.793285</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6799310538701273</v>
+        <v>0.6813534535594252</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2065300156957832</v>
+        <v>0.2055615431361976</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1135389304340896</v>
+        <v>0.1130850033043772</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.6799310538701273</v>
+        <v>0.6813534535594252</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2.044999186009309</v>
+        <v>2.035035875127534</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5278001231378084</v>
+        <v>0.5291143634425087</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.03880237348518445</v>
+        <v>0.03772253481573773</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.07935082219243128</v>
+        <v>0.07676671165077376</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2.044999186009309</v>
+        <v>2.035035875127534</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.5278001231378084</v>
+        <v>0.5291143634425087</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.03880237348518445</v>
+        <v>0.03772253481573773</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.07935082219243128</v>
+        <v>0.07676671165077376</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.123368489608657</v>
+        <v>0.1233507871487831</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>0.1135171265774146</v>
+        <v>0.1131956871631794</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>0.1064800888183439</v>
+        <v>0.1061975054804946</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>0.09693472002517582</v>
+        <v>0.0969367319435441</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>0.08236005526880043</v>
+        <v>0.08256907321405484</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>0.07119301692520212</v>
+        <v>0.070829947488463</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.06471303105083126</v>
+        <v>0.064887920879852</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.04123730495564813</v>
+        <v>0.04145282739382507</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>0.03865280616183241</v>
+        <v>0.03842130100875794</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.03808241462696751</v>
+        <v>0.03808946102857207</v>
       </c>
     </row>
     <row r="3">
@@ -1114,31 +1114,31 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.575736796370891</v>
+        <v>2.57486745731466</v>
       </c>
       <c r="L3" t="n">
-        <v>0.751512237229276</v>
+        <v>0.7523815762855075</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8849543574355543</v>
+        <v>0.884128398772496</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08167465408017752</v>
+        <v>0.08190561471766766</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03337098848426825</v>
+        <v>0.03396598650983633</v>
       </c>
       <c r="Q3" t="n">
         <v>0.7146926312225738</v>
       </c>
       <c r="R3" t="n">
-        <v>2.965104799964138</v>
+        <v>2.963524183498263</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7348952000358621</v>
+        <v>0.7364758165017375</v>
       </c>
       <c r="T3" t="n">
         <v>0.7496178112088051</v>
@@ -1156,58 +1156,58 @@
         <v>0.4883352348298124</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7595501533215251</v>
+        <v>0.7592287604279423</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1610735146909105</v>
+        <v>0.1612177897543061</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0793763319875645</v>
+        <v>0.07955344981775134</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6459882357082236</v>
+        <v>0.6459883185613331</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3540117642917764</v>
+        <v>0.3540116814386669</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4950861005943888</v>
+        <v>0.4954354572958644</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5049138994056113</v>
+        <v>0.5045645427041356</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.759425</v>
+        <v>0.7590249999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.161945</v>
+        <v>0.162075</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.07863000000000001</v>
+        <v>0.0789</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.64712</v>
+        <v>0.6471</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.49575</v>
+        <v>0.49616</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.57555</v>
+        <v>2.574635</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.752885</v>
+        <v>0.753845</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.328435</v>
+        <v>3.32848</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8062355152276848</v>
+        <v>0.8058247835390659</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1316513973180618</v>
+        <v>0.1317798503389068</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.06211308745425344</v>
+        <v>0.0623953661220274</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.8062355152276848</v>
+        <v>0.8058247835390659</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>29.96614860454073</v>
+        <v>29.44121760486499</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.06211308745425344</v>
+        <v>0.0623953661220274</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.02874209896998518</v>
+        <v>0.02842937961219107</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.8612900089409929</v>
+        <v>0.8369955515338297</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1246,13 +1246,13 @@
         <v>3.504991841904088</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.3540117642917764</v>
+        <v>0.3540116814386669</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0687043955143502</v>
+        <v>0.06870431266124072</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.2408083457807493</v>
+        <v>0.2408080553812764</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1190698463551388</v>
+        <v>0.1189894573458196</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1022308615317198</v>
+        <v>0.1021273604944272</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.08948244662089651</v>
+        <v>0.08952547547920488</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>0.0855068746528807</v>
+        <v>0.08546996039373386</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.07682774346357908</v>
+        <v>0.07683874447067542</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.07642915333715078</v>
+        <v>0.07649172212524565</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>0.06582994794298705</v>
+        <v>0.06574110425963585</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.04947201145532096</v>
+        <v>0.04946239564961472</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04284268058031887</v>
+        <v>0.04284836025117741</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03391212384398639</v>
+        <v>0.0338549259932133</v>
       </c>
     </row>
     <row r="4">
